--- a/CNN/data/cf_summary.xlsx
+++ b/CNN/data/cf_summary.xlsx
@@ -458,13 +458,13 @@
         <v>575</v>
       </c>
       <c r="B2" t="n">
-        <v>5.813001418571905</v>
+        <v>5.936243363493455</v>
       </c>
       <c r="C2" t="n">
-        <v>5.718801508229772</v>
+        <v>5.770993356031307</v>
       </c>
       <c r="D2" t="n">
-        <v>5.813001418571905</v>
+        <v>5.858959670614715</v>
       </c>
     </row>
   </sheetData>
@@ -508,13 +508,13 @@
         <v>575</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8383582234382629</v>
+        <v>0.8561323285102844</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8247725963592529</v>
+        <v>0.8322997689247131</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8383582234382629</v>
+        <v>0.8449863791465759</v>
       </c>
     </row>
   </sheetData>
@@ -1124,7 +1124,7 @@
         <v>0.5159166666666637</v>
       </c>
       <c r="D2" t="n">
-        <v>72.16444444444444</v>
+        <v>72.16444605223506</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1136,7 +1136,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.693379185180734</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
@@ -1145,7 +1145,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>0.7068085475848462</v>
       </c>
       <c r="L2" t="n">
         <v>0.7656111111111247</v>
@@ -1154,7 +1154,7 @@
         <v>0.765611111111125</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2853661516958253</v>
+        <v>0.2853664904473551</v>
       </c>
       <c r="O2" t="n">
         <v>19</v>
@@ -1184,7 +1184,7 @@
         <v>198.4677777777778</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>0.09017052777777658</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -1196,7 +1196,7 @@
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>1000.000001841459</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -1205,7 +1205,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.54502777777778</v>
+        <v>0.545027936833245</v>
       </c>
       <c r="AF2" t="n">
         <v>0.5450277777777794</v>
@@ -1217,7 +1217,7 @@
         <v>20</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.5724061037264312</v>
+        <v>0.5724060901987114</v>
       </c>
       <c r="AJ2" t="n">
         <v>0.9359595000632508</v>
@@ -1229,7 +1229,7 @@
         <v>0.4869427863402407</v>
       </c>
       <c r="AM2" t="n">
-        <v>-0.05591666666666641</v>
+        <v>-0.05591665278488599</v>
       </c>
       <c r="AN2" t="n">
         <v>1</v>
@@ -1238,7 +1238,7 @@
         <v>0.5849999999999954</v>
       </c>
       <c r="AP2" t="n">
-        <v>286.041394688908</v>
+        <v>286.0413888888889</v>
       </c>
       <c r="AQ2" t="n">
         <v>0</v>
@@ -1250,7 +1250,7 @@
         <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>0.693379185180734</v>
       </c>
       <c r="AU2" t="n">
         <v>1000</v>
@@ -1277,7 +1277,7 @@
         <v>0.5529987137536569</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.9466272700119839</v>
+        <v>0.9466273291126273</v>
       </c>
       <c r="BD2" t="n">
         <v>1.097066666666665</v>
@@ -1295,7 +1295,7 @@
         <v>0.7086388888888834</v>
       </c>
       <c r="BI2" t="n">
-        <v>234.9</v>
+        <v>234.9000108932426</v>
       </c>
       <c r="BJ2" t="n">
         <v>0</v>
@@ -1325,19 +1325,19 @@
         <v>-0.5993888888888964</v>
       </c>
       <c r="BS2" t="n">
-        <v>-0.6614205850351594</v>
+        <v>-0.6614205564341921</v>
       </c>
       <c r="BT2" t="n">
-        <v>22</v>
+        <v>22.00000048</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.318508069083667</v>
+        <v>0.3185081318872357</v>
       </c>
       <c r="BV2" t="n">
         <v>0.7156926966711867</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.008758333333331</v>
+        <v>1.00875834318833</v>
       </c>
       <c r="BX2" t="n">
         <v>0.4995948574727662</v>
@@ -1352,7 +1352,7 @@
         <v>0.5485833333333288</v>
       </c>
       <c r="CB2" t="n">
-        <v>230.8258333333333</v>
+        <v>230.8258371880911</v>
       </c>
       <c r="CC2" t="n">
         <v>0</v>
@@ -1367,7 +1367,7 @@
         <v>0</v>
       </c>
       <c r="CG2" t="n">
-        <v>1000</v>
+        <v>999.9999998338263</v>
       </c>
       <c r="CH2" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.1056400420036336</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.3302423933501112</v>
+        <v>0.3302423937242363</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.874727777777775</v>
+        <v>0.8747277739715527</v>
       </c>
       <c r="CQ2" t="n">
         <v>0.4087711302178467</v>
@@ -1409,13 +1409,13 @@
         <v>0.8357499999999981</v>
       </c>
       <c r="CU2" t="n">
-        <v>191.7230555555555</v>
+        <v>191.7230669709808</v>
       </c>
       <c r="CV2" t="n">
         <v>0</v>
       </c>
       <c r="CW2" t="n">
-        <v>0</v>
+        <v>0.09583472222222207</v>
       </c>
       <c r="CX2" t="n">
         <v>0</v>
@@ -1427,7 +1427,7 @@
         <v>1000</v>
       </c>
       <c r="DA2" t="n">
-        <v>0</v>
+        <v>0.693379185180734</v>
       </c>
       <c r="DB2" t="n">
         <v>0</v>
@@ -1477,7 +1477,7 @@
         <v>72.16444444444444</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.09017052777777658</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1507,19 +1507,19 @@
         <v>0.2853661516958253</v>
       </c>
       <c r="O3" t="n">
-        <v>19</v>
+        <v>18.99999985</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7136101293297098</v>
+        <v>0.7136101442494762</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.9464631811522527</v>
+        <v>0.9464631627214413</v>
       </c>
       <c r="R3" t="n">
         <v>1.318316666666665</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5434181647840812</v>
+        <v>0.5434181484137373</v>
       </c>
       <c r="T3" t="n">
         <v>0.5450277777777794</v>
@@ -1579,16 +1579,16 @@
         <v>0.4869427863402407</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.05591666666666641</v>
+        <v>-0.05591665278488599</v>
       </c>
       <c r="AN3" t="n">
         <v>1</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.5849999999999954</v>
+        <v>0.5849999855363708</v>
       </c>
       <c r="AP3" t="n">
-        <v>286.0413888888889</v>
+        <v>286.0413882954599</v>
       </c>
       <c r="AQ3" t="n">
         <v>0</v>
@@ -1609,7 +1609,7 @@
         <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>0.7068085475848462</v>
       </c>
       <c r="AX3" t="n">
         <v>-0.05591666666666617</v>
@@ -1618,7 +1618,7 @@
         <v>-0.05591666666666632</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.4985626525097475</v>
+        <v>-0.4985624283751994</v>
       </c>
       <c r="BA3" t="n">
         <v>21</v>
@@ -1642,7 +1642,7 @@
         <v>1</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.7086388888888834</v>
+        <v>0.7086389023916916</v>
       </c>
       <c r="BI3" t="n">
         <v>234.9</v>
@@ -1663,13 +1663,13 @@
         <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>0.693379185180734</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>0.7068085475848462</v>
       </c>
       <c r="BQ3" t="n">
-        <v>-0.5993888888888967</v>
+        <v>-0.5993888979753487</v>
       </c>
       <c r="BR3" t="n">
         <v>-0.5993888888888964</v>
@@ -1684,7 +1684,7 @@
         <v>0.318508069083667</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.7156926966711867</v>
+        <v>0.7156927264289817</v>
       </c>
       <c r="BW3" t="n">
         <v>1.008758333333331</v>
@@ -1693,7 +1693,7 @@
         <v>0.4995948574727662</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.8581944444444446</v>
+        <v>-0.8581938012728758</v>
       </c>
       <c r="BZ3" t="n">
         <v>1</v>
@@ -1702,7 +1702,7 @@
         <v>0.5485833333333288</v>
       </c>
       <c r="CB3" t="n">
-        <v>230.8258333333333</v>
+        <v>230.8258307946429</v>
       </c>
       <c r="CC3" t="n">
         <v>0</v>
@@ -1729,7 +1729,7 @@
         <v>-0.8581944444444443</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0.8581944444444445</v>
+        <v>-0.8581945133192368</v>
       </c>
       <c r="CL3" t="n">
         <v>0.2891464646904749</v>
@@ -1738,7 +1738,7 @@
         <v>23</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.1056400420036336</v>
+        <v>0.1056400473300854</v>
       </c>
       <c r="CO3" t="n">
         <v>0.3302423933501112</v>
@@ -1750,7 +1750,7 @@
         <v>0.4087711302178467</v>
       </c>
       <c r="CR3" t="n">
-        <v>11.97641666666701</v>
+        <v>11.97641689179274</v>
       </c>
       <c r="CS3" t="n">
         <v>0.9000000000000571</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="DB3" t="n">
-        <v>0</v>
+        <v>0.7068085475848462</v>
       </c>
       <c r="DC3" t="n">
         <v>11.97641666666701</v>
@@ -1795,10 +1795,10 @@
         <v>1</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.0010924845096889</v>
+        <v>0.001092484492801704</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.003454739468963401</v>
+        <v>0.003454739366070726</v>
       </c>
       <c r="DI3" t="n">
         <v>0.7943499999999972</v>
@@ -2764,7 +2764,7 @@
         <v>0</v>
       </c>
       <c r="DM2" t="n">
-        <v>5.813001418571905</v>
+        <v>5.936243363493455</v>
       </c>
     </row>
     <row r="3">
@@ -2778,7 +2778,7 @@
         <v>0.5159166666666637</v>
       </c>
       <c r="D3" t="n">
-        <v>72.16444444444444</v>
+        <v>72.16444605223506</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -2790,7 +2790,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.693379185180734</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
@@ -2799,7 +2799,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.7068085475848462</v>
       </c>
       <c r="L3" t="n">
         <v>0.7656111111111247</v>
@@ -2808,7 +2808,7 @@
         <v>0.765611111111125</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2853661516958253</v>
+        <v>0.2853664904473551</v>
       </c>
       <c r="O3" t="n">
         <v>19</v>
@@ -2838,7 +2838,7 @@
         <v>198.4677777777778</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.09017052777777658</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -2850,7 +2850,7 @@
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>1000.000001841459</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -2859,7 +2859,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.54502777777778</v>
+        <v>0.545027936833245</v>
       </c>
       <c r="AF3" t="n">
         <v>0.5450277777777794</v>
@@ -2871,7 +2871,7 @@
         <v>20</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.5724061037264312</v>
+        <v>0.5724060901987114</v>
       </c>
       <c r="AJ3" t="n">
         <v>0.9359595000632508</v>
@@ -2883,7 +2883,7 @@
         <v>0.4869427863402407</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.05591666666666641</v>
+        <v>-0.05591665278488599</v>
       </c>
       <c r="AN3" t="n">
         <v>1</v>
@@ -2892,7 +2892,7 @@
         <v>0.5849999999999954</v>
       </c>
       <c r="AP3" t="n">
-        <v>286.041394688908</v>
+        <v>286.0413888888889</v>
       </c>
       <c r="AQ3" t="n">
         <v>0</v>
@@ -2904,7 +2904,7 @@
         <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>0.693379185180734</v>
       </c>
       <c r="AU3" t="n">
         <v>1000</v>
@@ -2931,7 +2931,7 @@
         <v>0.5529987137536569</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.9466272700119839</v>
+        <v>0.9466273291126273</v>
       </c>
       <c r="BD3" t="n">
         <v>1.097066666666665</v>
@@ -2949,7 +2949,7 @@
         <v>0.7086388888888834</v>
       </c>
       <c r="BI3" t="n">
-        <v>234.9</v>
+        <v>234.9000108932426</v>
       </c>
       <c r="BJ3" t="n">
         <v>0</v>
@@ -2979,19 +2979,19 @@
         <v>-0.5993888888888964</v>
       </c>
       <c r="BS3" t="n">
-        <v>-0.6614205850351594</v>
+        <v>-0.6614205564341921</v>
       </c>
       <c r="BT3" t="n">
-        <v>22</v>
+        <v>22.00000048</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.318508069083667</v>
+        <v>0.3185081318872357</v>
       </c>
       <c r="BV3" t="n">
         <v>0.7156926966711867</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.008758333333331</v>
+        <v>1.00875834318833</v>
       </c>
       <c r="BX3" t="n">
         <v>0.4995948574727662</v>
@@ -3006,7 +3006,7 @@
         <v>0.5485833333333288</v>
       </c>
       <c r="CB3" t="n">
-        <v>230.8258333333333</v>
+        <v>230.8258371880911</v>
       </c>
       <c r="CC3" t="n">
         <v>0</v>
@@ -3021,7 +3021,7 @@
         <v>0</v>
       </c>
       <c r="CG3" t="n">
-        <v>1000</v>
+        <v>999.9999998338263</v>
       </c>
       <c r="CH3" t="n">
         <v>0</v>
@@ -3045,10 +3045,10 @@
         <v>0.1056400420036336</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.3302423933501112</v>
+        <v>0.3302423937242363</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.874727777777775</v>
+        <v>0.8747277739715527</v>
       </c>
       <c r="CQ3" t="n">
         <v>0.4087711302178467</v>
@@ -3063,13 +3063,13 @@
         <v>0.8357499999999981</v>
       </c>
       <c r="CU3" t="n">
-        <v>191.7230555555555</v>
+        <v>191.7230669709808</v>
       </c>
       <c r="CV3" t="n">
         <v>0</v>
       </c>
       <c r="CW3" t="n">
-        <v>0</v>
+        <v>0.09583472222222207</v>
       </c>
       <c r="CX3" t="n">
         <v>0</v>
@@ -3081,7 +3081,7 @@
         <v>1000</v>
       </c>
       <c r="DA3" t="n">
-        <v>0</v>
+        <v>0.693379185180734</v>
       </c>
       <c r="DB3" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
         <v>1</v>
       </c>
       <c r="DM3" t="n">
-        <v>5.718801508229772</v>
+        <v>5.770993356031307</v>
       </c>
     </row>
     <row r="4">
@@ -3134,7 +3134,7 @@
         <v>72.16444444444444</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.09017052777777658</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -3164,19 +3164,19 @@
         <v>0.2853661516958253</v>
       </c>
       <c r="O4" t="n">
-        <v>19</v>
+        <v>18.99999985</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7136101293297098</v>
+        <v>0.7136101442494762</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9464631811522527</v>
+        <v>0.9464631627214413</v>
       </c>
       <c r="R4" t="n">
         <v>1.318316666666665</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5434181647840812</v>
+        <v>0.5434181484137373</v>
       </c>
       <c r="T4" t="n">
         <v>0.5450277777777794</v>
@@ -3236,16 +3236,16 @@
         <v>0.4869427863402407</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0.05591666666666641</v>
+        <v>-0.05591665278488599</v>
       </c>
       <c r="AN4" t="n">
         <v>1</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.5849999999999954</v>
+        <v>0.5849999855363708</v>
       </c>
       <c r="AP4" t="n">
-        <v>286.0413888888889</v>
+        <v>286.0413882954599</v>
       </c>
       <c r="AQ4" t="n">
         <v>0</v>
@@ -3266,7 +3266,7 @@
         <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>0.7068085475848462</v>
       </c>
       <c r="AX4" t="n">
         <v>-0.05591666666666617</v>
@@ -3275,7 +3275,7 @@
         <v>-0.05591666666666632</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-0.4985626525097475</v>
+        <v>-0.4985624283751994</v>
       </c>
       <c r="BA4" t="n">
         <v>21</v>
@@ -3299,7 +3299,7 @@
         <v>1</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.7086388888888834</v>
+        <v>0.7086389023916916</v>
       </c>
       <c r="BI4" t="n">
         <v>234.9</v>
@@ -3320,13 +3320,13 @@
         <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>0.693379185180734</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>0.7068085475848462</v>
       </c>
       <c r="BQ4" t="n">
-        <v>-0.5993888888888967</v>
+        <v>-0.5993888979753487</v>
       </c>
       <c r="BR4" t="n">
         <v>-0.5993888888888964</v>
@@ -3341,7 +3341,7 @@
         <v>0.318508069083667</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.7156926966711867</v>
+        <v>0.7156927264289817</v>
       </c>
       <c r="BW4" t="n">
         <v>1.008758333333331</v>
@@ -3350,7 +3350,7 @@
         <v>0.4995948574727662</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.8581944444444446</v>
+        <v>-0.8581938012728758</v>
       </c>
       <c r="BZ4" t="n">
         <v>1</v>
@@ -3359,7 +3359,7 @@
         <v>0.5485833333333288</v>
       </c>
       <c r="CB4" t="n">
-        <v>230.8258333333333</v>
+        <v>230.8258307946429</v>
       </c>
       <c r="CC4" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
         <v>-0.8581944444444443</v>
       </c>
       <c r="CK4" t="n">
-        <v>-0.8581944444444445</v>
+        <v>-0.8581945133192368</v>
       </c>
       <c r="CL4" t="n">
         <v>0.2891464646904749</v>
@@ -3395,7 +3395,7 @@
         <v>23</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.1056400420036336</v>
+        <v>0.1056400473300854</v>
       </c>
       <c r="CO4" t="n">
         <v>0.3302423933501112</v>
@@ -3407,7 +3407,7 @@
         <v>0.4087711302178467</v>
       </c>
       <c r="CR4" t="n">
-        <v>11.97641666666701</v>
+        <v>11.97641689179274</v>
       </c>
       <c r="CS4" t="n">
         <v>0.9000000000000571</v>
@@ -3437,7 +3437,7 @@
         <v>0</v>
       </c>
       <c r="DB4" t="n">
-        <v>0</v>
+        <v>0.7068085475848462</v>
       </c>
       <c r="DC4" t="n">
         <v>11.97641666666701</v>
@@ -3452,10 +3452,10 @@
         <v>1</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.0010924845096889</v>
+        <v>0.001092484492801704</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.003454739468963401</v>
+        <v>0.003454739366070726</v>
       </c>
       <c r="DI4" t="n">
         <v>0.7943499999999972</v>
@@ -3470,7 +3470,7 @@
         <v>2</v>
       </c>
       <c r="DM4" t="n">
-        <v>5.813001418571905</v>
+        <v>5.858959670614715</v>
       </c>
     </row>
   </sheetData>
